--- a/Data/2023TdxCs/StocksCode.xlsx
+++ b/Data/2023TdxCs/StocksCode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12345"/>
+    <workbookView windowWidth="20490" windowHeight="7950"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15000" uniqueCount="10003">
   <si>
-    <t>MArket</t>
+    <t>Market</t>
   </si>
   <si>
     <t>StockCode</t>
   </si>
   <si>
-    <t>StockNAme</t>
+    <t>StockName</t>
   </si>
   <si>
     <t>SZ</t>
